--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/KENTUCKY_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/KENTUCKY_2023.xlsx
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C129">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C226">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C233">
